--- a/products.xlsx
+++ b/products.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="600" firstSheet="3" activeTab="11" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Drinks" sheetId="1" state="visible" r:id="rId1"/>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1123,6 +1123,54 @@
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Qoshiq</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>90</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sanchiqi</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>piece</t>
         </is>

--- a/products.xlsx
+++ b/products.xlsx
@@ -650,7 +650,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9000</v>
@@ -706,7 +706,7 @@
         <v>12000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -946,7 +946,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,6 +1171,54 @@
         <v>10</v>
       </c>
       <c r="F4" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Qozon</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>190000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Tovoq</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>piece</t>
         </is>
@@ -1188,7 +1236,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1336,7 +1384,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1532,7 +1580,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1680,7 +1728,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1804,7 +1852,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -1928,7 +1976,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2052,7 +2100,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2176,7 +2224,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
